--- a/LubanConfig/MiniTemplate/Datas/基础数据/#玩家操作评估.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#玩家操作评估.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
   <si>
     <t>##type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,6 +144,14 @@
   </si>
   <si>
     <t>玩家10分钟获得经验值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作容错率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -219,7 +227,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -255,11 +263,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -286,6 +305,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -568,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.25" customWidth="1"/>
@@ -828,6 +850,17 @@
         <v>18</v>
       </c>
     </row>
+    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#玩家操作评估.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#玩家操作评估.xlsx
@@ -858,7 +858,7 @@
         <v>34</v>
       </c>
       <c r="C20">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
